--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="152">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,68 +260,52 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.code</t>
+    <t>Identifiant</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.dureeTraitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Durée du traitement</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.frequenceAdministration</t>
+  </si>
+  <si>
+    <t>Fréquence d'administration</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.nombreRenouvellement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Nombre de renouvellement(s) possible(s)</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.voieAdministration</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Acte ou situation</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Partie narrative de l’entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut de l’entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.dureeTraitement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Durée du traitement</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.frequenceAdministration</t>
-  </si>
-  <si>
-    <t>Fréquence d'administration</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.nombreRenouvellement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integer
-</t>
-  </si>
-  <si>
-    <t>Nombre de renouvellement(s) possible(s)</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.voieAdministration</t>
-  </si>
-  <si>
     <t>Voie d'administration</t>
   </si>
   <si>
@@ -391,26 +375,6 @@
   </si>
   <si>
     <t>Motif du traitement (Référence interne)</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.traitementPrescritSubordonnee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitement-prescrit-subordonne
-</t>
-  </si>
-  <si>
-    <t>Traitement prescrit subordonnée</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.referenceItemPlanTraitement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-reference-item-plan-traitement
-</t>
-  </si>
-  <si>
-    <t>Référence à un item du plan de traitement</t>
   </si>
   <si>
     <t>fr-lm-traitement-prescrit.instructionsPatient</t>
@@ -828,11 +792,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ32"/>
+  <dimension ref="A1:AJ28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.3984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.3984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.83984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.83984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -862,7 +826,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.3984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="44.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1191,7 +1155,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>79</v>
@@ -1266,7 +1230,7 @@
         <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>79</v>
@@ -1291,7 +1255,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>79</v>
@@ -1366,7 +1330,7 @@
         <v>85</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>79</v>
@@ -1391,7 +1355,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>79</v>
@@ -1406,13 +1370,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1466,7 +1430,7 @@
         <v>88</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>79</v>
@@ -1480,10 +1444,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1506,13 +1470,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L7" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1563,7 +1527,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1580,10 +1544,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1606,7 +1570,7 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>95</v>
@@ -1663,7 +1627,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1694,7 +1658,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1706,13 +1670,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1769,7 +1733,7 @@
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1780,10 +1744,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1806,7 +1770,7 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>100</v>
@@ -1863,7 +1827,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1894,7 +1858,7 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1906,13 +1870,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1969,7 +1933,7 @@
         <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
@@ -1980,10 +1944,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1994,7 +1958,7 @@
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -2006,7 +1970,7 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>105</v>
@@ -2063,13 +2027,13 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
@@ -2091,7 +2055,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
@@ -2166,7 +2130,7 @@
         <v>106</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>79</v>
@@ -2194,7 +2158,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2206,13 +2170,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2269,7 +2233,7 @@
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2280,10 +2244,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2291,7 +2255,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>79</v>
@@ -2306,7 +2270,7 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>113</v>
@@ -2363,10 +2327,10 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>79</v>
@@ -2394,7 +2358,7 @@
         <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
@@ -2469,7 +2433,7 @@
         <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>73</v>
@@ -2506,13 +2470,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2580,10 +2544,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2594,7 +2558,7 @@
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>73</v>
@@ -2606,13 +2570,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2663,13 +2627,13 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>73</v>
@@ -2680,10 +2644,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2694,7 +2658,7 @@
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -2706,13 +2670,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2763,13 +2727,13 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>73</v>
@@ -2780,10 +2744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2791,10 +2755,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2806,13 +2770,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2863,13 +2827,13 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
@@ -2880,10 +2844,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2906,13 +2870,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2963,7 +2927,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -2980,10 +2944,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2991,7 +2955,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -3006,13 +2970,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3063,10 +3027,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -3080,10 +3044,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3091,7 +3055,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -3106,13 +3070,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3163,10 +3127,10 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>79</v>
@@ -3180,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3206,13 +3170,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3263,7 +3227,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3280,10 +3244,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3291,7 +3255,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -3306,13 +3270,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3363,10 +3327,10 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -3380,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3406,13 +3370,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3463,7 +3427,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3480,10 +3444,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3491,10 +3455,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -3506,13 +3470,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3563,13 +3527,13 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>73</v>
@@ -3580,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3591,7 +3555,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>79</v>
@@ -3606,7 +3570,7 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>151</v>
@@ -3663,10 +3627,10 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>79</v>
@@ -3675,406 +3639,6 @@
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q29" s="2"/>
-      <c r="R29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q30" s="2"/>
-      <c r="R30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="143">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -273,6 +273,36 @@
     <t>Statut</t>
   </si>
   <si>
+    <t>fr-lm-traitement-prescrit.produitSante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-produit-sante
+</t>
+  </si>
+  <si>
+    <t>Produit de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.indication[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+string</t>
+  </si>
+  <si>
+    <t>Motif du traitement</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.finaliteTherapeutique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Objet de la prescription - prophylaxie, traitement, anesthésie, etc</t>
+  </si>
+  <si>
     <t>fr-lm-traitement-prescrit.dureeTraitement</t>
   </si>
   <si>
@@ -283,10 +313,62 @@
     <t>Durée du traitement</t>
   </si>
   <si>
-    <t>fr-lm-traitement-prescrit.frequenceAdministration</t>
-  </si>
-  <si>
-    <t>Fréquence d'administration</t>
+    <t>fr-lm-traitement-prescrit.posologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-posologie
+</t>
+  </si>
+  <si>
+    <t>Posologie</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.quantiteProduit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-quantite-produit
+</t>
+  </si>
+  <si>
+    <t>Quantite de produit</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.periodeValiditeLignePrescription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {organization-period}
+</t>
+  </si>
+  <si>
+    <t>Periode de validité de la ligne de prescription</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.autorisationSubstitution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>Autorisation de substitution</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.autorisationSubstitution.allowed[x]</t>
+  </si>
+  <si>
+    <t>Type de substitution jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis (2.16.840.1.113883.1.11.16621)</t>
+  </si>
+  <si>
+    <t>HL7_SubstanceAdminSubstitution</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.autorisationSubstitution.reason[x]</t>
+  </si>
+  <si>
+    <t>Motif de non substitution (Marge thérapeutique étroite, Enfant forme galénique, Contre-indication formelle).</t>
   </si>
   <si>
     <t>fr-lm-traitement-prescrit.nombreRenouvellement</t>
@@ -299,56 +381,24 @@
     <t>Nombre de renouvellement(s) possible(s)</t>
   </si>
   <si>
-    <t>fr-lm-traitement-prescrit.voieAdministration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
+    <t>fr-lm-traitement-prescrit.horsAMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-hors-amm
 </t>
   </si>
   <si>
-    <t>Voie d'administration</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.regionAnatomique</t>
-  </si>
-  <si>
-    <t>région anatomique d'administration</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.dose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
+    <t>Hors AMM</t>
+  </si>
+  <si>
+    <t>fr-lm-traitement-prescrit.instructionsDispensateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Dose à administrer</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.rythmeAdministration[x]</t>
-  </si>
-  <si>
-    <t>Ratio
-Quantity</t>
-  </si>
-  <si>
-    <t>Rythme d'administration</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.doseMaximale[x]</t>
-  </si>
-  <si>
-    <t>Dose maximale</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.produitSante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-produit-sante
-</t>
-  </si>
-  <si>
-    <t>Produit de santé</t>
+    <t>Instructions au dispensateur</t>
   </si>
   <si>
     <t>fr-lm-traitement-prescrit.prescripteur</t>
@@ -367,66 +417,6 @@
     <t>Auteur du document Prescription</t>
   </si>
   <si>
-    <t>fr-lm-traitement-prescrit.motifTraitement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-reference-interne
-</t>
-  </si>
-  <si>
-    <t>Motif du traitement (Référence interne)</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.instructionsPatient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-instructions-patient
-</t>
-  </si>
-  <si>
-    <t>Instructions au patient</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.instructionsDispensateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-instructions-au-dispensateur
-</t>
-  </si>
-  <si>
-    <t>Instructions au dispensateur</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.quantiteProduit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-quantite-produit
-</t>
-  </si>
-  <si>
-    <t>Quantite de produit</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.autorisationSubstitution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-autorisation-substitution
-</t>
-  </si>
-  <si>
-    <t>Autorisation de substitution</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.periodeRenouvellement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-periode-de-renouvellement
-</t>
-  </si>
-  <si>
-    <t>Periode de renouvellement</t>
-  </si>
-  <si>
     <t>fr-lm-traitement-prescrit.enRapportAvecALD</t>
   </si>
   <si>
@@ -467,30 +457,10 @@
     <t>Non remboursable</t>
   </si>
   <si>
-    <t>fr-lm-traitement-prescrit.horsAMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-hors-amm
-</t>
-  </si>
-  <si>
-    <t>Hors AMM</t>
-  </si>
-  <si>
     <t>fr-lm-traitement-prescrit.referencePrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Base
-</t>
-  </si>
-  <si>
     <t>Référence de la prescription</t>
-  </si>
-  <si>
-    <t>fr-lm-traitement-prescrit.precondition</t>
-  </si>
-  <si>
-    <t>Précondition à l'utilisation du médicament</t>
   </si>
 </sst>
 </file>
@@ -792,11 +762,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ28"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.83984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.83984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.21875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.21875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -819,14 +789,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="27.48046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.33984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="48.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1255,7 +1225,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>79</v>
@@ -1330,7 +1300,7 @@
         <v>85</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>79</v>
@@ -1358,7 +1328,7 @@
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1370,13 +1340,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1433,7 +1403,7 @@
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1444,10 +1414,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1470,13 +1440,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1527,7 +1497,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1544,10 +1514,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1570,13 +1540,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1627,7 +1597,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1644,10 +1614,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1655,10 +1625,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1670,13 +1640,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1727,13 +1697,13 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1744,10 +1714,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1770,13 +1740,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1827,7 +1797,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1844,10 +1814,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1870,13 +1840,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1927,7 +1897,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1944,10 +1914,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1955,10 +1925,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -1970,13 +1940,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2027,13 +1997,13 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
@@ -2044,10 +2014,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2055,7 +2025,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
@@ -2070,13 +2040,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2106,10 +2076,10 @@
         <v>73</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>73</v>
@@ -2127,10 +2097,10 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>79</v>
@@ -2144,10 +2114,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2170,13 +2140,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2227,7 +2197,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2244,10 +2214,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2270,13 +2240,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2327,7 +2297,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2344,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2355,10 +2325,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
@@ -2370,13 +2340,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2427,13 +2397,13 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>73</v>
@@ -2444,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2470,13 +2440,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2527,7 +2497,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2544,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2570,13 +2540,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2627,7 +2597,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2644,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2670,13 +2640,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2727,7 +2697,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2744,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2770,13 +2740,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2827,7 +2797,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2844,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2855,7 +2825,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2870,13 +2840,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2927,10 +2897,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -2944,10 +2914,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2970,13 +2940,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3027,7 +2997,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3044,10 +3014,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3070,13 +3040,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3127,7 +3097,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3144,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3155,10 +3125,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
@@ -3170,13 +3140,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3227,418 +3197,18 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q25" s="2"/>
-      <c r="R25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q26" s="2"/>
-      <c r="R26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q27" s="2"/>
-      <c r="R27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q28" s="2"/>
-      <c r="R28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-traitement-prescrit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
